--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -4,25 +4,38 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="9735"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -32,7 +45,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -44,7 +57,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -53,7 +66,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -65,37 +78,10 @@
   </si>
   <si>
     <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>平台SKU</t>
-    </r>
-  </si>
-  <si>
-    <t>FNSKU</t>
-  </si>
-  <si>
-    <t>平台产品名称</t>
-  </si>
-  <si>
-    <t>规格信息</t>
-  </si>
-  <si>
-    <t>包装信息</t>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -104,7 +90,41 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平台SKU</t>
+    </r>
+  </si>
+  <si>
+    <t>FNSKU</t>
+  </si>
+  <si>
+    <t>平台产品名称</t>
+  </si>
+  <si>
+    <t>规格信息</t>
+  </si>
+  <si>
+    <t>包装信息</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -127,6 +147,9 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>{.platformName}</t>
   </si>
   <si>
@@ -134,7 +157,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -144,7 +167,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -154,7 +177,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -197,11 +220,14 @@
   <si>
     <t>{.createTime}</t>
   </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -212,20 +238,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -233,7 +259,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -241,14 +267,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -256,7 +282,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -264,7 +290,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -272,7 +298,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -280,7 +306,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -288,14 +314,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -303,7 +329,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -311,7 +337,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -319,14 +345,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -334,42 +360,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -824,7 +850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -846,63 +872,60 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1200,23 +1223,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="27.8761904761905" customWidth="1"/>
-    <col min="2" max="2" width="20.5047619047619" customWidth="1"/>
-    <col min="3" max="3" width="20.5047619047619" customWidth="1"/>
-    <col min="4" max="6" width="20.5047619047619" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.8761904761905" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5047619047619" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32.6285714285714" style="1" customWidth="1"/>
-    <col min="10" max="11" width="21.752380952381" customWidth="1"/>
-    <col min="12" max="12" width="19.1238095238095" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27.875" customWidth="1"/>
+    <col min="2" max="3" width="20.5083333333333" customWidth="1"/>
+    <col min="4" max="6" width="20.5083333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5083333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32.625" style="1" customWidth="1"/>
+    <col min="10" max="11" width="21.75" customWidth="1"/>
+    <col min="12" max="12" width="19.125" style="2" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="18.6285714285714" customWidth="1"/>
+    <col min="14" max="14" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:14">
+    <row r="1" ht="35.25" customHeight="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1244,10 +1266,10 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1259,49 +1281,55 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>14</v>
+    <row r="2" ht="21" customHeight="1" spans="1:15">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1343,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1327,7 +1355,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <r>
       <rPr>
@@ -71,6 +71,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>店铺名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售员</t>
     </r>
   </si>
   <si>
@@ -183,6 +197,9 @@
       </rPr>
       <t>}</t>
     </r>
+  </si>
+  <si>
+    <t>{.sellerName}</t>
   </si>
   <si>
     <t>{.platformSpuNo}</t>
@@ -1223,35 +1240,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
-    <col min="2" max="3" width="20.5083333333333" customWidth="1"/>
-    <col min="4" max="6" width="20.5083333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5083333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="21.75" customWidth="1"/>
-    <col min="12" max="12" width="19.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="18.625" customWidth="1"/>
+    <col min="2" max="4" width="20.5083333333333" customWidth="1"/>
+    <col min="5" max="7" width="20.5083333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5083333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="21.75" customWidth="1"/>
+    <col min="13" max="13" width="19.125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:15">
+    <row r="1" ht="35.25" customHeight="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
@@ -1263,16 +1280,16 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -1284,52 +1301,58 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:15">
+    <row r="2" ht="21" customHeight="1" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <r>
       <rPr>
@@ -75,6 +75,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -155,10 +162,13 @@
     <t>匹配关系</t>
   </si>
   <si>
+    <t>开始时间</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>创建人</t>
-  </si>
-  <si>
-    <t>创建时间</t>
   </si>
   <si>
     <t>备注</t>
@@ -230,6 +240,12 @@
   </si>
   <si>
     <t>{.matchResultStr}</t>
+  </si>
+  <si>
+    <t>{.effectiveTime}</t>
+  </si>
+  <si>
+    <t>{.expireTime}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1240,7 +1256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1250,12 +1266,12 @@
     <col min="9" max="9" width="22.5083333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="32.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="21.75" customWidth="1"/>
-    <col min="13" max="13" width="19.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="18.625" customWidth="1"/>
+    <col min="13" max="15" width="19.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:16">
+    <row r="1" ht="35.25" customHeight="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1304,55 +1320,67 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:16">
+    <row r="2" ht="21" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <r>
       <rPr>
@@ -165,10 +165,13 @@
     <t>开始时间</t>
   </si>
   <si>
+    <t>结束时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
     <t>创建时间</t>
-  </si>
-  <si>
-    <t>创建人</t>
   </si>
   <si>
     <t>备注</t>
@@ -1321,66 +1324,66 @@
         <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <r>
       <rPr>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>系统创建时间</t>
   </si>
   <si>
     <t>{.platformName}</t>
@@ -258,6 +261,9 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.systemCreateTime}</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1272,9 +1278,10 @@
     <col min="13" max="15" width="19.125" style="2" customWidth="1"/>
     <col min="16" max="16" width="22" customWidth="1"/>
     <col min="17" max="17" width="18.625" customWidth="1"/>
+    <col min="19" max="19" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:18">
+    <row r="1" ht="35.25" customHeight="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1329,61 +1336,67 @@
       <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:18">
+    <row r="2" ht="21" customHeight="1" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <r>
       <rPr>
@@ -166,6 +166,24 @@
   </si>
   <si>
     <t>结束时间</t>
+  </si>
+  <si>
+    <t>NCM</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>跨州CFOP</t>
+  </si>
+  <si>
+    <t>同州CFOP</t>
+  </si>
+  <si>
+    <t>原产地</t>
+  </si>
+  <si>
+    <t>开票产品名称</t>
   </si>
   <si>
     <t>创建人</t>
@@ -252,6 +270,24 @@
   </si>
   <si>
     <t>{.expireTime}</t>
+  </si>
+  <si>
+    <t>{.invoiceHsCode}</t>
+  </si>
+  <si>
+    <t>{.unit}</t>
+  </si>
+  <si>
+    <t>{.diffStateTaxCode}</t>
+  </si>
+  <si>
+    <t>{.sameStateTaxCode}</t>
+  </si>
+  <si>
+    <t>{.dictOriginName}</t>
+  </si>
+  <si>
+    <t>{.invoiceProductName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -892,7 +928,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -916,6 +952,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1265,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
@@ -1275,13 +1314,13 @@
     <col min="9" max="9" width="22.5083333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="32.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="21.75" customWidth="1"/>
-    <col min="13" max="15" width="19.125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
-    <col min="17" max="17" width="18.625" customWidth="1"/>
-    <col min="19" max="19" width="18.625" customWidth="1"/>
+    <col min="13" max="21" width="19.125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="18.625" customWidth="1"/>
+    <col min="25" max="25" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:19">
+    <row r="1" ht="35.25" customHeight="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1339,64 +1378,100 @@
       <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:19">
+    <row r="2" ht="21" customHeight="1" spans="1:25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <r>
       <rPr>
@@ -123,7 +123,13 @@
     <t>FNSKU</t>
   </si>
   <si>
+    <t>父平台产品ID</t>
+  </si>
+  <si>
     <t>平台产品名称</t>
+  </si>
+  <si>
+    <t>状态</t>
   </si>
   <si>
     <t>规格信息</t>
@@ -245,7 +251,13 @@
     <t>{.platformFnSku}</t>
   </si>
   <si>
+    <t>{.platformParenSkutId}</t>
+  </si>
+  <si>
     <t>{.platformProductName}</t>
+  </si>
+  <si>
+    <t>{.platformStatusName}</t>
   </si>
   <si>
     <t>{.productSpec}</t>
@@ -1304,23 +1316,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="27.875" customWidth="1"/>
     <col min="2" max="4" width="20.5083333333333" customWidth="1"/>
-    <col min="5" max="7" width="20.5083333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5083333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="32.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="21.75" customWidth="1"/>
-    <col min="13" max="21" width="19.125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="22" customWidth="1"/>
-    <col min="23" max="23" width="18.625" customWidth="1"/>
+    <col min="5" max="8" width="20.5083333333333" style="1" customWidth="1"/>
+    <col min="9" max="10" width="22.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5083333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="32.625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="21.75" customWidth="1"/>
+    <col min="15" max="23" width="19.125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="22" customWidth="1"/>
     <col min="25" max="25" width="18.625" customWidth="1"/>
+    <col min="27" max="27" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:25">
+    <row r="1" ht="35.25" customHeight="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1348,19 +1360,19 @@
       <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1381,13 +1393,13 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="3" t="s">
@@ -1396,82 +1408,94 @@
       <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:25">
+    <row r="2" ht="21" customHeight="1" spans="1:27">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="K2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="M2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/PlatformSkuMapping.xlsx
@@ -251,7 +251,7 @@
     <t>{.platformFnSku}</t>
   </si>
   <si>
-    <t>{.platformParenSkutId}</t>
+    <t>{.platformParentSpuNo}</t>
   </si>
   <si>
     <t>{.platformProductName}</t>
